--- a/Output/resumo_executivo_terca.xlsx
+++ b/Output/resumo_executivo_terca.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>Qtd_Projetos</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Percentagem do Total</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -453,6 +458,11 @@
       <c r="D2" t="n">
         <v>2</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>23.7%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -469,6 +479,11 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -485,6 +500,11 @@
       <c r="D4" t="n">
         <v>2</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41.0%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -500,6 +520,11 @@
       </c>
       <c r="D5" t="n">
         <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
       </c>
     </row>
   </sheetData>
